--- a/exports/trend_1d/KALYANKJIL_full_report.xlsx
+++ b/exports/trend_1d/KALYANKJIL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:U41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>17.67</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44316</v>
+        <v>44319</v>
       </c>
       <c r="H2" t="n">
-        <v>59.9</v>
+        <v>58.65</v>
       </c>
       <c r="I2" t="n">
         <v>58.995265</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>-13.56</v>
+        <v>-15.37</v>
       </c>
       <c r="L2" t="n">
-        <v>13.78</v>
+        <v>15.51</v>
       </c>
       <c r="M2" t="n">
         <v>1.6</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>13.55</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44340</v>
+        <v>44341</v>
       </c>
       <c r="H3" t="n">
-        <v>63</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>64.84185207652305</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>-7.42</v>
+        <v>-15.69</v>
       </c>
       <c r="L3" t="n">
-        <v>10.66</v>
+        <v>16.62</v>
       </c>
       <c r="M3" t="n">
         <v>1.66</v>
       </c>
       <c r="N3" t="n">
-        <v>4.59</v>
+        <v>7.7</v>
       </c>
       <c r="O3" t="n">
         <v>-2.09</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>14.84</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44393</v>
+        <v>44396</v>
       </c>
       <c r="H4" t="n">
-        <v>75</v>
+        <v>72.8</v>
       </c>
       <c r="I4" t="n">
         <v>74.84147475693821</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K4" t="n">
-        <v>10.54</v>
+        <v>7.3</v>
       </c>
       <c r="L4" t="n">
         <v>6.41</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.37</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44453</v>
+        <v>44454</v>
       </c>
       <c r="H5" t="n">
-        <v>66.65000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="I5" t="n">
         <v>68.44413787637886</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K5" t="n">
-        <v>8.449999999999999</v>
+        <v>2.06</v>
       </c>
       <c r="L5" t="n">
         <v>3.98</v>
@@ -726,7 +785,7 @@
         <v>1.72</v>
       </c>
       <c r="N5" t="n">
-        <v>6.59</v>
+        <v>6.98</v>
       </c>
       <c r="O5" t="n">
         <v>-2.93</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.9</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H6" t="n">
-        <v>72.84999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="I6" t="n">
         <v>72.70531746917101</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K6" t="n">
-        <v>2.17</v>
+        <v>-3.93</v>
       </c>
       <c r="L6" t="n">
         <v>6.03</v>
@@ -783,7 +854,7 @@
         <v>2.5</v>
       </c>
       <c r="N6" t="n">
-        <v>3.14</v>
+        <v>5.97</v>
       </c>
       <c r="O6" t="n">
         <v>6.98</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>16.44</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H7" t="n">
-        <v>70.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>72.52594487820338</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.5</v>
+        <v>-6.72</v>
       </c>
       <c r="L7" t="n">
-        <v>7.66</v>
+        <v>10.8</v>
       </c>
       <c r="M7" t="n">
         <v>1.81</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>9.84</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H8" t="n">
-        <v>67.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>65.90686006541075</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>-7.25</v>
+        <v>-10.94</v>
       </c>
       <c r="L8" t="n">
-        <v>8.07</v>
+        <v>11.29</v>
       </c>
       <c r="M8" t="n">
         <v>1.98</v>
       </c>
       <c r="N8" t="n">
-        <v>1.96</v>
+        <v>3.98</v>
       </c>
       <c r="O8" t="n">
         <v>3.1</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.76</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H9" t="n">
-        <v>61.9</v>
+        <v>64.5</v>
       </c>
       <c r="I9" t="n">
         <v>62.67903328809192</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K9" t="n">
-        <v>4.92</v>
+        <v>0.92</v>
       </c>
       <c r="L9" t="n">
         <v>9.83</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>11.89</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44687</v>
+        <v>44690</v>
       </c>
       <c r="H10" t="n">
-        <v>60.2</v>
+        <v>59.3</v>
       </c>
       <c r="I10" t="n">
         <v>59.77776503536684</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.67</v>
+        <v>-8.06</v>
       </c>
       <c r="L10" t="n">
         <v>9.609999999999999</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>9.4</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44748</v>
+        <v>44749</v>
       </c>
       <c r="H11" t="n">
-        <v>61.2</v>
+        <v>63.65</v>
       </c>
       <c r="I11" t="n">
         <v>62.04679872701436</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.2</v>
+        <v>-7.34</v>
       </c>
       <c r="L11" t="n">
         <v>14.17</v>
       </c>
       <c r="M11" t="n">
-        <v>2.33</v>
+        <v>3.76</v>
       </c>
       <c r="N11" t="n">
         <v>5.13</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44886</v>
+        <v>44887</v>
       </c>
       <c r="H12" t="n">
-        <v>96</v>
+        <v>91.2</v>
       </c>
       <c r="I12" t="n">
         <v>95.95679052739889</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K12" t="n">
-        <v>50.82</v>
+        <v>43.28</v>
       </c>
       <c r="L12" t="n">
         <v>2.04</v>
@@ -1125,7 +1268,7 @@
         <v>1.97</v>
       </c>
       <c r="N12" t="n">
-        <v>4.26</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>4</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>14.66</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44894</v>
+        <v>44895</v>
       </c>
       <c r="H13" t="n">
-        <v>98.95</v>
+        <v>105.9</v>
       </c>
       <c r="I13" t="n">
         <v>104.5744162558796</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.5</v>
+        <v>-16.12</v>
       </c>
       <c r="L13" t="n">
-        <v>11.07</v>
+        <v>19.63</v>
       </c>
       <c r="M13" t="n">
         <v>1.42</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>13.85</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H14" t="n">
-        <v>122.65</v>
+        <v>107.7</v>
       </c>
       <c r="I14" t="n">
         <v>113.6490561435241</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K14" t="n">
-        <v>15.82</v>
+        <v>1.7</v>
       </c>
       <c r="L14" t="n">
         <v>5.57</v>
       </c>
       <c r="M14" t="n">
-        <v>0.26</v>
+        <v>0.57</v>
       </c>
       <c r="N14" t="n">
-        <v>5.65</v>
+        <v>12.19</v>
       </c>
       <c r="O14" t="n">
         <v>7.02</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>26.38</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45078</v>
+        <v>45079</v>
       </c>
       <c r="H15" t="n">
-        <v>108.7</v>
+        <v>112.65</v>
       </c>
       <c r="I15" t="n">
         <v>109.6603812828722</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.93</v>
+        <v>-4.6</v>
       </c>
       <c r="L15" t="n">
         <v>24.61</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>7</v>
+      </c>
+      <c r="U15" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.49</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45189</v>
+        <v>45190</v>
       </c>
       <c r="H16" t="n">
-        <v>219.15</v>
+        <v>213.1</v>
       </c>
       <c r="I16" t="n">
         <v>215.9080278555706</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K16" t="n">
-        <v>94.54000000000001</v>
+        <v>89.17</v>
       </c>
       <c r="L16" t="n">
         <v>3.42</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>18.31</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45204</v>
+        <v>45205</v>
       </c>
       <c r="H17" t="n">
-        <v>234.4</v>
+        <v>258.15</v>
       </c>
       <c r="I17" t="n">
         <v>245.7177359059392</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>-10</v>
+        <v>-21.14</v>
       </c>
       <c r="L17" t="n">
-        <v>10.63</v>
+        <v>22.48</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.26</v>
       </c>
       <c r="N17" t="n">
-        <v>6.05</v>
+        <v>10.13</v>
       </c>
       <c r="O17" t="n">
         <v>-2.76</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>16.97</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="H18" t="n">
-        <v>350.2</v>
+        <v>334.05</v>
       </c>
       <c r="I18" t="n">
         <v>345.6803845541499</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K18" t="n">
-        <v>35.66</v>
+        <v>29.4</v>
       </c>
       <c r="L18" t="n">
         <v>7.15</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>18.24</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45336</v>
+        <v>45337</v>
       </c>
       <c r="H19" t="n">
-        <v>364.25</v>
+        <v>391.65</v>
       </c>
       <c r="I19" t="n">
         <v>386.5628414827581</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K19" t="n">
-        <v>-9.039999999999999</v>
+        <v>-17.24</v>
       </c>
       <c r="L19" t="n">
-        <v>10.7</v>
+        <v>22.65</v>
       </c>
       <c r="M19" t="n">
         <v>3.78</v>
       </c>
       <c r="N19" t="n">
-        <v>4.39</v>
+        <v>7.52</v>
       </c>
       <c r="O19" t="n">
         <v>-4.61</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>16.83</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H20" t="n">
-        <v>390.95</v>
+        <v>378.65</v>
       </c>
       <c r="I20" t="n">
         <v>383.7994049672137</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.18</v>
+        <v>-3.32</v>
       </c>
       <c r="L20" t="n">
-        <v>10.09</v>
+        <v>14.2</v>
       </c>
       <c r="M20" t="n">
         <v>2.01</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>11.89</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45457</v>
+        <v>45461</v>
       </c>
       <c r="H21" t="n">
-        <v>400.5</v>
+        <v>424</v>
       </c>
       <c r="I21" t="n">
         <v>423.6698489905524</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.77</v>
+        <v>-11.98</v>
       </c>
       <c r="L21" t="n">
-        <v>10.92</v>
+        <v>13.63</v>
       </c>
       <c r="M21" t="n">
         <v>1.94</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>14.14</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45589</v>
+        <v>45590</v>
       </c>
       <c r="H22" t="n">
-        <v>696.1</v>
+        <v>671.7</v>
       </c>
       <c r="I22" t="n">
         <v>674.6650344191426</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K22" t="n">
-        <v>64.17</v>
+        <v>58.42</v>
       </c>
       <c r="L22" t="n">
         <v>5.93</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>16.27</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45632</v>
+        <v>45635</v>
       </c>
       <c r="H23" t="n">
-        <v>730.5</v>
+        <v>775.45</v>
       </c>
       <c r="I23" t="n">
         <v>735.3264395164194</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.75</v>
+        <v>-15.45</v>
       </c>
       <c r="L23" t="n">
-        <v>11.66</v>
+        <v>15.93</v>
       </c>
       <c r="M23" t="n">
         <v>2.32</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>13.72</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="H24" t="n">
-        <v>706.4</v>
+        <v>662.55</v>
       </c>
       <c r="I24" t="n">
         <v>699.7425837174684</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.9</v>
+        <v>-14.56</v>
       </c>
       <c r="L24" t="n">
-        <v>14.44</v>
+        <v>15.4</v>
       </c>
       <c r="M24" t="n">
         <v>1.99</v>
       </c>
       <c r="N24" t="n">
-        <v>4.27</v>
+        <v>6.21</v>
       </c>
       <c r="O24" t="n">
         <v>6.15</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>20.34</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45691</v>
+        <v>45692</v>
       </c>
       <c r="H25" t="n">
-        <v>502.9</v>
+        <v>563.8</v>
       </c>
       <c r="I25" t="n">
         <v>557.271784385264</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K25" t="n">
-        <v>24.1</v>
+        <v>14.9</v>
       </c>
       <c r="L25" t="n">
         <v>7.07</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>26.5</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45722</v>
+        <v>45723</v>
       </c>
       <c r="H26" t="n">
-        <v>450.4</v>
+        <v>431.7</v>
       </c>
       <c r="I26" t="n">
         <v>439.0216489460598</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K26" t="n">
-        <v>-20.11</v>
+        <v>-23.43</v>
       </c>
       <c r="L26" t="n">
         <v>24.44</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>20.66</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="H27" t="n">
-        <v>458.05</v>
+        <v>511.1</v>
       </c>
       <c r="I27" t="n">
         <v>497.4890500679135</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.1</v>
+        <v>-18.39</v>
       </c>
       <c r="L27" t="n">
-        <v>15.98</v>
+        <v>20.08</v>
       </c>
       <c r="M27" t="n">
         <v>1.46</v>
       </c>
       <c r="N27" t="n">
-        <v>4.4</v>
+        <v>11.58</v>
       </c>
       <c r="O27" t="n">
         <v>-4.15</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>19.39</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45819</v>
+        <v>45820</v>
       </c>
       <c r="H28" t="n">
-        <v>535.2</v>
+        <v>518.55</v>
       </c>
       <c r="I28" t="n">
         <v>519.0350580180854</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K28" t="n">
-        <v>4.72</v>
+        <v>1.46</v>
       </c>
       <c r="L28" t="n">
         <v>13.31</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>10.31</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45835</v>
+        <v>45838</v>
       </c>
       <c r="H29" t="n">
-        <v>544.75</v>
+        <v>555.85</v>
       </c>
       <c r="I29" t="n">
         <v>555.5824481153525</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.05</v>
+        <v>-7.19</v>
       </c>
       <c r="L29" t="n">
-        <v>7.5</v>
+        <v>7.81</v>
       </c>
       <c r="M29" t="n">
         <v>0.51</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>9.6</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="H30" t="n">
-        <v>590.95</v>
+        <v>528.1</v>
       </c>
       <c r="I30" t="n">
         <v>562.2205950155884</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K30" t="n">
-        <v>6.31</v>
+        <v>-4.99</v>
       </c>
       <c r="L30" t="n">
-        <v>2.45</v>
+        <v>7.25</v>
       </c>
       <c r="M30" t="n">
         <v>2.66</v>
       </c>
       <c r="N30" t="n">
-        <v>3.1</v>
+        <v>10.64</v>
       </c>
       <c r="O30" t="n">
         <v>2.04</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>21.71</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="H31" t="n">
-        <v>495.3</v>
+        <v>505.85</v>
       </c>
       <c r="I31" t="n">
         <v>495.5874335546969</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K31" t="n">
-        <v>6.21</v>
+        <v>4.21</v>
       </c>
       <c r="L31" t="n">
         <v>16.64</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>8.74</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="H32" t="n">
-        <v>496.45</v>
+        <v>484.4</v>
       </c>
       <c r="I32" t="n">
         <v>484.8641029229083</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.86</v>
+        <v>-4.24</v>
       </c>
       <c r="L32" t="n">
-        <v>3.91</v>
+        <v>4.9</v>
       </c>
       <c r="M32" t="n">
         <v>0.44</v>
       </c>
       <c r="N32" t="n">
-        <v>1.97</v>
+        <v>2.43</v>
       </c>
       <c r="O32" t="n">
         <v>2.13</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>9.26</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="H33" t="n">
-        <v>500.15</v>
+        <v>520.75</v>
       </c>
       <c r="I33" t="n">
         <v>507.3576288067499</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.25</v>
+        <v>-7.5</v>
       </c>
       <c r="L33" t="n">
-        <v>6.52</v>
+        <v>10.45</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7</v>
+        <v>0.97</v>
       </c>
       <c r="N33" t="n">
-        <v>3.06</v>
+        <v>4.12</v>
       </c>
       <c r="O33" t="n">
         <v>-2.43</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>8.25</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="H34" t="n">
-        <v>480.4</v>
+        <v>467.5</v>
       </c>
       <c r="I34" t="n">
         <v>477.7771050130848</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K34" t="n">
-        <v>-7.75</v>
+        <v>-10.23</v>
       </c>
       <c r="L34" t="n">
-        <v>8.69</v>
+        <v>11.09</v>
       </c>
       <c r="M34" t="n">
         <v>0.49</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>10.75</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="H35" t="n">
-        <v>380.25</v>
+        <v>437.35</v>
       </c>
       <c r="I35" t="n">
         <v>421.2452726909425</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>18.66</v>
+        <v>6.45</v>
       </c>
       <c r="L35" t="n">
         <v>2.87</v>
       </c>
       <c r="M35" t="n">
-        <v>6.16</v>
+        <v>6.51</v>
       </c>
       <c r="N35" t="n">
-        <v>5.05</v>
+        <v>15.02</v>
       </c>
       <c r="O35" t="n">
         <v>-2.69</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>20.39</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="H36" t="n">
-        <v>382.7</v>
+        <v>362.7</v>
       </c>
       <c r="I36" t="n">
         <v>369.3247703137722</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K36" t="n">
-        <v>-12.5</v>
+        <v>-17.07</v>
       </c>
       <c r="L36" t="n">
-        <v>15.19</v>
+        <v>17.43</v>
       </c>
       <c r="M36" t="n">
         <v>3.69</v>
       </c>
       <c r="N36" t="n">
-        <v>4.11</v>
+        <v>5.23</v>
       </c>
       <c r="O36" t="n">
         <v>15.02</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>13.86</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="H37" t="n">
-        <v>394.35</v>
+        <v>420.35</v>
       </c>
       <c r="I37" t="n">
         <v>412.1023703186498</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K37" t="n">
-        <v>-8.73</v>
+        <v>-15.89</v>
       </c>
       <c r="L37" t="n">
-        <v>9.529999999999999</v>
+        <v>16.34</v>
       </c>
       <c r="M37" t="n">
         <v>3.39</v>
       </c>
       <c r="N37" t="n">
-        <v>5.42</v>
+        <v>6.59</v>
       </c>
       <c r="O37" t="n">
         <v>-5.23</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>14.95</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="H38" t="n">
-        <v>424.55</v>
+        <v>385.2</v>
       </c>
       <c r="I38" t="n">
         <v>396.1531022621781</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>6.03</v>
+        <v>9.1</v>
       </c>
       <c r="M38" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="N38" t="n">
-        <v>3.05</v>
+        <v>9.27</v>
       </c>
       <c r="O38" t="n">
         <v>6.59</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>15.37</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="H39" t="n">
-        <v>344.75</v>
+        <v>383</v>
       </c>
       <c r="I39" t="n">
         <v>375.2463459371889</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K39" t="n">
-        <v>10.5</v>
+        <v>0.57</v>
       </c>
       <c r="L39" t="n">
         <v>6.7</v>
@@ -2664,7 +3131,7 @@
         <v>2.18</v>
       </c>
       <c r="N39" t="n">
-        <v>4.22</v>
+        <v>11.09</v>
       </c>
       <c r="O39" t="n">
         <v>-9.27</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>17.07</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="H40" t="n">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="I40" t="n">
         <v>564.9407847857075</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K40" t="n">
-        <v>49.61</v>
+        <v>47.26</v>
       </c>
       <c r="L40" t="n">
         <v>9.050000000000001</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2781,6 +3272,14 @@
       <c r="Q41" t="n">
         <v>21</v>
       </c>
+      <c r="R41" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5223,7 +5722,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="6">
@@ -5233,7 +5732,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -5243,7 +5742,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8">
@@ -5253,7 +5752,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -5263,7 +5762,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65.5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -5273,7 +5772,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>111.4</v>
+        <v>112.4</v>
       </c>
     </row>
     <row r="11">
@@ -5283,7 +5782,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -5293,7 +5792,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -5303,7 +5802,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>43.6</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="14">
@@ -5313,7 +5812,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.39</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="15">
@@ -5323,7 +5822,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12.83</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5832,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.39</v>
+        <v>-7.17</v>
       </c>
     </row>
     <row r="17">
@@ -5343,7 +5842,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>94.54000000000001</v>
+        <v>89.17</v>
       </c>
     </row>
     <row r="18">
@@ -5353,7 +5852,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43.6</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="19">
@@ -5363,7 +5862,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.6</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="20">
@@ -5373,7 +5872,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.050000000000001</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="21">
@@ -5393,7 +5892,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -5403,7 +5902,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -5413,7 +5912,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="25">
@@ -5433,7 +5932,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.22</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="27">
@@ -5443,7 +5942,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14.17</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="28">
@@ -5453,7 +5952,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
